--- a/output/output.xlsx
+++ b/output/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,35 +509,20 @@
           <t>0c2f9fc842a866ee.pdf</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>S600100040138</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>S600100040138</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO CORRECTIVO DE
-CANALETAS Y COBERTURA DE TECHOS</t>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO CORRECTIVO DE CANALETAS Y COBERTURA DE TECHOS</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -560,29 +545,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0cca4ed1c20922e1.pdf</t>
+          <t>0c2f9fc842a866ee.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -605,37 +584,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0cca4ed1c20922e1.pdf</t>
+          <t>0c2f9fc842a866ee.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>in DE POLICARBONATO</t>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>in DE POLICARBONATO</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>diámetro: nominal de 300 mm</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
@@ -654,42 +623,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0cca4ed1c20922e1.pdf</t>
+          <t>0c2f9fc842a866ee.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE
-POLICARBONATO
- Nombre comercial: Óptico para semáforo ciclista.
- Año de fabricación: Mínimo 2022
- Emitirá 02 señales: Rojo Estático y Verde Dinámico.
- Diámetro</t>
+          <t>MEDIDA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO  Nombre comercial: Óptico para semáforo ciclista.  Año de fabricación: Mínimo 2022  Emitirá 02 señales: Rojo Estático y Verde Dinámico.  Diámetro</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>MEDIDA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>diámetro: nominal de la unidad óptica 300 mm</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
@@ -704,6 +658,3511 @@
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Calaminon tipo TI 1107mm. x 11.80 ml.), a ambos lados de la canaleta, encausando el agua de</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Calaminon tipo TI 1107mm. x 11.80 ml.), a ambos lados de la canaleta, encausando el agua de</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.2. MATERIALES, EQUIPOS E INSTALACIONES:</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4.2. MATERIALES, EQUIPOS E INSTALACIONES:</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>una altura de 25 m. aproximadamente. Además de contar con un prevencionista de riesgo a</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>una altura de 25 m. aproximadamente. Además de contar con un prevencionista de riesgo a</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.3. DOCUMENTACIÓN PREVIA AL INICIO DEL SERVICIO:</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4.3. DOCUMENTACIÓN PREVIA AL INICIO DEL SERVICIO:</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4.4. CONDICIONES DEL SERVICIO:</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4.4. CONDICIONES DEL SERVICIO:</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.5. RESULTADOS ESPERADOS:</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4.5. RESULTADOS ESPERADOS:</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>• Una (01) Constancia y/o Certificado de la limpieza realizada al cobertor y a las canaletas.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>• Una (01) Constancia y/o Certificado de la limpieza realizada al cobertor y a las canaletas.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>• Un (01) Informe técnico del servicio realizado, en físico, con fotografías que lo sustenten. Este</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>• Un (01) Informe técnico del servicio realizado, en físico, con fotografías que lo sustenten. Este</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>será por cuadruplicado (04), refrendado por el profesional responsable.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>será por cuadruplicado (04), refrendado por el profesional responsable.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.6. LUGAR, PLAZO Y HORARIO DE LA PRESTACIÓN DEL SERVICIO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4.6. LUGAR, PLAZO Y HORARIO DE LA PRESTACIÓN DEL SERVICIO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Castilla, ubicado en Jr. Huallaga N° 656, cercado de Lima.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Castilla, ubicado en Jr. Huallaga N° 656, cercado de Lima.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>La ejecución del servicio se realizará en un plazo de hasta diez (10) días calendario,</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>La ejecución del servicio se realizará en un plazo de hasta diez (10) días calendario,</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>El servicio se ejecutara entre las 07:00 horas hasta las 22:00 horas, previa coordinación</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>El servicio se ejecutara entre las 07:00 horas hasta las 22:00 horas, previa coordinación</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5. REQUISITOS DEL PROVEEDOR Y SU PERSONAL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5. REQUISITOS DEL PROVEEDOR Y SU PERSONAL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5.1. Requisitos del Proveedor:</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5.1. Requisitos del Proveedor:</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>acumulado equivalente a S/ 10 000.00 (Diez mil con 00/100 soles), mediante copia simple de</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>acumulado equivalente a S/ 10 000.00 (Diez mil con 00/100 soles), mediante copia simple de</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5.2. Perfil del personal requerido para el servicio:</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5.2. Perfil del personal requerido para el servicio:</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>*Nota: Se precisa que de no presentar la documentación de los numerales 5.1 y 5.2, no será válida su</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>*Nota: Se precisa que de no presentar la documentación de los numerales 5.1 y 5.2, no será válida su</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6. MEDIDAS DE CONTROL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6. MEDIDAS DE CONTROL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6.2. Área que brinda la conformidad: Conformidad:</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6.2. Área que brinda la conformidad: Conformidad:</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7.1. Alcance de la garantía: Por defectos en la ejecución del servicio.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7.1. Alcance de la garantía: Por defectos en la ejecución del servicio.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7.2. Período de garantía: El periodo de garantía será de seis (06) meses a partir del día siguiente de</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>7.2. Período de garantía: El periodo de garantía será de seis (06) meses a partir del día siguiente de</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7.3. Procedimiento para hacer efectiva la garantía: El área usuaria informará a la Oficina de Logística,</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>7.3. Procedimiento para hacer efectiva la garantía: El área usuaria informará a la Oficina de Logística,</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7.4. Tiempo de subsanación: Dentro de los tres (03) días calendario de recibida la notificación.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>7.4. Tiempo de subsanación: Dentro de los tres (03) días calendario de recibida la notificación.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>hasta un máximo equivalente al 10% del importe contratado o prestación parcial, según la Directiva N°</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hasta un máximo equivalente al 10% del importe contratado o prestación parcial, según la Directiva N°</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>002-2024-MML, en el numeral 8.10 de las penalidades.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>002-2024-MML, en el numeral 8.10 de las penalidades.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F = 0.25 para plazos mayores a sesenta (60) días o;</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>F = 0.25 para plazos mayores a sesenta (60) días o;</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F = 0.40 para plazos menores o iguales a sesenta (60) días.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>F = 0.40 para plazos menores o iguales a sesenta (60) días.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Penalidad Total = Penalidad Diaria x Cantidad de días de atraso</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Penalidad Total = Penalidad Diaria x Cantidad de días de atraso</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mediante deposito en cuenta interbancaria aproximadamente a los 15 días de otorgada la Conformidad.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mediante deposito en cuenta interbancaria aproximadamente a los 15 días de otorgada la Conformidad.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10. PLAZO POR VICIOS OCULTOS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10. PLAZO POR VICIOS OCULTOS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>El plazo máximo de responsabilidad del contratista es de seis (06) meses contados a partir de la</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>El plazo máximo de responsabilidad del contratista es de seis (06) meses contados a partir de la</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11. OTRAS OBLIGACIONES DEL PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11. OTRAS OBLIGACIONES DEL PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>comunicado con un (01) día antes de su ingreso, mediante correo electrónico a la coordinadora del</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>comunicado con un (01) día antes de su ingreso, mediante correo electrónico a la coordinadora del</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>11.1. SEGUROS APLICABLES</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>11.1. SEGUROS APLICABLES</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>(aprobado mediante Decreto Supremo Nº 005-2012-TR); la misma será presentada a partir del</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(aprobado mediante Decreto Supremo Nº 005-2012-TR); la misma será presentada a partir del</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>12. DECLARACIÓN DE ANTICORRUPCION</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12. DECLARACIÓN DE ANTICORRUPCION</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/S</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/S</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1. Por incumplimiento injustificado de las obligaciones contractuales, legales o reglamentarias a su</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1. Por incumplimiento injustificado de las obligaciones contractuales, legales o reglamentarias a su</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2. Por acumulación del monto máximo de la penalidad por mora o del monto máximo para otras</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2. Por acumulación del monto máximo de la penalidad por mora o del monto máximo para otras</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3. Por la paralización o reducción injustificada de la ejecución de la prestación, pese a haber sido</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3. Por la paralización o reducción injustificada de la ejecución de la prestación, pese a haber sido</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4. Por caso fortuito o fuerza mayor que imposibilite de manera definitiva la continuidad de la ejecución,</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4. Por caso fortuito o fuerza mayor que imposibilite de manera definitiva la continuidad de la ejecución,</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5. Por mutuo acuerdo entre las partes; las partes pueden resolver de forma total o parcial la O/C u</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>5. Por mutuo acuerdo entre las partes; las partes pueden resolver de forma total o parcial la O/C u</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14. SOLUCIÓN DE CONTROVERSIAS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>14. SOLUCIÓN DE CONTROVERSIAS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>15. CONFIDENCIALIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>15. CONFIDENCIALIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>16. PROPIEDAD INTELECTUAL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>16. PROPIEDAD INTELECTUAL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>realice el contratista en virtud de la presente contratación, corresponden en su totalidad a la</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>realice el contratista en virtud de la presente contratación, corresponden en su totalidad a la</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0c2f9fc842a866ee.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Av. Inca Garcilaso de la Vega 1348 – 4° piso - Lima</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4. PERFIL TÉCNICO MÍNIMO DEL PROVEEDOR DEL BIEN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4. PERFIL TÉCNICO MÍNIMO DEL PROVEEDOR DEL BIEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>acumulado equivalente a S/30.000 (Treinta Mil 00/100 soles), mediante copia simple de</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>acumulado equivalente a S/30.000 (Treinta Mil 00/100 soles), mediante copia simple de</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>30.000</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>30</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>El plazo máximo de entrega será a los (15) días calendarios contabilizados a partir del día</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>El plazo máximo de entrega será a los (15) días calendarios contabilizados a partir del día</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ubicado en Vía de Evitamiento Km 6.5, Rímac – Sede Acho, previa coordinación con el área</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ubicado en Vía de Evitamiento Km 6.5, Rímac – Sede Acho, previa coordinación con el área</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>8.1. ALCANCE DE LA GARANTÍA:</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>8.1. ALCANCE DE LA GARANTÍA:</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>8.2. PERIODO DE GARANTÍA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>8.2. PERIODO DE GARANTÍA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>El certificado de garantía comercial por los productos entregados, deberá ser de doce (12)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>El certificado de garantía comercial por los productos entregados, deberá ser de doce (12)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>8.3. TIEMPO DE REPOSICIÓN DEL BIEN:</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>8.3. TIEMPO DE REPOSICIÓN DEL BIEN:</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>plazo máximo de diez (10) días calendario, el cual será contabilizado desde el día siguiente</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>plazo máximo de diez (10) días calendario, el cual será contabilizado desde el día siguiente</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jr. Cuzco N° 286-11º Piso – Cercado de Lima</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Jr. Cuzco N° 286-11º Piso – Cercado de Lima</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2. Por acumulación del monto máximo de la penalidad por mora o del monto máximo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2. Por acumulación del monto máximo de la penalidad por mora o del monto máximo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3. Por la paralización o reducción injustificada de la ejecución de la prestación, pese a</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3. Por la paralización o reducción injustificada de la ejecución de la prestación, pese a</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4. Por caso fortuito o fuerza mayor que imposibilite de manera definitiva la continuidad</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>4. Por caso fortuito o fuerza mayor que imposibilite de manera definitiva la continuidad</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>5. Por mutuo acuerdo entre las partes; las partes pueden resolver de forma total o</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>5. Por mutuo acuerdo entre las partes; las partes pueden resolver de forma total o</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>14. SOLUCIÓN DE CONTROVERSIAS</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>14. SOLUCIÓN DE CONTROVERSIAS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>15. CONFIDENCIALIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>15. CONFIDENCIALIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0cca4ed1c20922e1.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jr. Cuzco N° 286-11º Piso – Cercado de Lima</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Jr. Cuzco N° 286-11º Piso – Cercado de Lima</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/output.xlsx
+++ b/output/output.xlsx
@@ -3097,7 +3097,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3106,11 +3106,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3138,30 +3134,22 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO  Nombre comercial: Óptico para semáforo ciclista.  Año de fabricación: Mínimo 2022  Emitirá 02 señales: Rojo Estático y Verde Dinámico.  Diámetro nominal de la unidad óptica 300 mm  IMPORTANTE: El óptico para semáforo ciclista 300 mm, debe cumplir con las Características Específicas descritas en el numeral 3.2.1.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO  Nombre comercial: Óptico para semáforo ciclista.  Año de fabricación: Mínimo 2022  Emitirá 02 señales: Rojo Estático y Verde Dinámico.  Diámetro nominal de la unidad óptica 300 mm  IMPORTANTE: El óptico para semáforo ciclista 300 mm, debe cumplir con las Características Específicas descritas en el numeral 3.2.1.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3667,16 +3655,8 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -3714,16 +3694,8 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -3761,16 +3733,8 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -3808,16 +3772,8 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>

--- a/output/output.xlsx
+++ b/output/output.xlsx
@@ -525,7 +525,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -564,7 +568,11 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -603,7 +611,11 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -642,7 +654,11 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -734,7 +750,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -781,7 +801,11 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -828,7 +852,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -875,7 +903,11 @@
           <t>134</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -922,7 +954,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -969,7 +1005,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1016,7 +1056,11 @@
           <t>01</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1063,7 +1107,11 @@
           <t>01</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1110,7 +1158,11 @@
           <t>04</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1157,7 +1209,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1204,7 +1260,11 @@
           <t>656</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1251,7 +1311,11 @@
           <t>134</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1298,7 +1362,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1345,7 +1413,11 @@
           <t>07</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1392,7 +1464,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1439,7 +1515,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -1531,7 +1611,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1578,7 +1662,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1625,7 +1713,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1672,7 +1764,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1719,7 +1815,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -1766,7 +1866,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -1813,7 +1917,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -1860,7 +1968,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -1907,7 +2019,11 @@
           <t>134</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -1954,7 +2070,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2128,7 +2248,11 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2175,7 +2299,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2222,7 +2350,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2269,7 +2401,11 @@
           <t>06</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2316,7 +2452,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2363,7 +2503,11 @@
           <t>01</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -2410,7 +2554,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2457,7 +2605,11 @@
           <t>005</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2504,7 +2656,11 @@
           <t>134</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -2551,7 +2707,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -2598,7 +2758,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -2645,7 +2809,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -2692,7 +2860,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -2739,7 +2911,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -2786,7 +2962,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -2833,7 +3013,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -2880,7 +3064,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -2927,7 +3115,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -2974,7 +3166,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -3013,7 +3209,11 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3060,7 +3260,11 @@
           <t>134</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -3097,7 +3301,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3106,8 +3310,16 @@
           <t>01</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SEMÁFORO LED DE TRÁFICO 1 X 12 in DE POLICARBONATO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3148,9 +3360,21 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -3197,7 +3421,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -3289,7 +3517,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3336,7 +3568,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3383,7 +3619,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -3430,7 +3670,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -3477,7 +3721,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -3524,7 +3772,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -3571,7 +3823,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -3618,7 +3874,11 @@
           <t>286</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -3655,9 +3915,21 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios a contratar se encuentran en el listado de bienes y servicios comunes de la Subasta Inversa Electrónica</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -3694,9 +3966,21 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en algún catálogo del Acuerdo Marco</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -3733,9 +4017,21 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Los bienes o servicios se encuentran en las fichas de homologación</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3772,9 +4068,21 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>13. RESOLUCIÓN DE CONTRATO U O/C</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -3821,7 +4129,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -3868,7 +4180,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -3915,7 +4231,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -3962,7 +4282,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -4009,7 +4333,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4056,7 +4384,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4103,7 +4435,11 @@
           <t>286</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
